--- a/results/full_birds_summary/birds_PartialAbstention_summary.xlsx
+++ b/results/full_birds_summary/birds_PartialAbstention_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:BU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,100 +476,320 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>afrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>arec__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arec__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>arec__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arec__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>rec__0.0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>rec__0.1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>rec__0.2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>rec__0.3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.3</t>
         </is>
@@ -623,100 +843,320 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.3254±0.0535</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.2934±0.0881</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.2867±0.0443</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.2894±0.0515</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.9881±0.0024</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.9738±0.0053</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.9176±0.0087</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.7894±0.0105</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.8232±0.0615</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.5821±0.0860</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.2547±0.0487</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.1134±0.0215</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.7456±0.0418</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.6122±0.0881</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.4005±0.0722</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.3011±0.0447</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0.7624±0.0474</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.5750±0.0798</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.2924±0.0529</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.1552±0.0262</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.9471±0.0079</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>0.8927±0.0158</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.7722±0.0144</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.6670±0.0137</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.7086±0.0432</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.5207±0.0740</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.2348±0.0452</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.1044±0.0182</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.4797±0.0591</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.4347±0.0565</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.2839±0.0362</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.1720±0.0262</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.5256±0.0861</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.4013±0.0519</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.2047±0.0326</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.1105±0.0202</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.4698±0.0444</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.5327±0.0770</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.5731±0.0714</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.5407±0.0671</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.9653±0.0894</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.8407±0.1145</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.7402±0.1197</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.7839±0.0363</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.6451±0.0561</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3821±0.0480</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.2047±0.0366</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.8205±0.0517</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.5603±0.0677</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.2595±0.0408</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.1223±0.0250</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.7517±0.0332</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.7678±0.0623</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.7363±0.0408</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.6444±0.0392</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>0.8419±0.0233</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.7085±0.0445</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.3265±0.0488</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>0.0195±0.0120</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>0.5185±0.0476</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.3492±0.0708</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.0833±0.0310</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.0041±0.0059</t>
         </is>
@@ -770,100 +1210,320 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>0.3203±0.0534</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.2823±0.0785</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.2843±0.0463</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.2806±0.0428</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.9879±0.0025</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.9728±0.0053</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.9139±0.0098</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.7809±0.0104</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.8215±0.0613</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.5735±0.0858</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.2487±0.0475</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.1110±0.0206</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.7492±0.0440</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6180±0.0890</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.4032±0.0737</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.3067±0.0448</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.7633±0.0485</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.5728±0.0792</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.2882±0.0524</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.1535±0.0255</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.9463±0.0087</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.8886±0.0166</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.7619±0.0147</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6535±0.0129</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.7102±0.0443</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.5173±0.0726</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.2300±0.0445</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.1027±0.0175</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.4846±0.0576</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.4373±0.0537</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.2805±0.0365</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.1705±0.0254</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.5311±0.0881</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.3974±0.0525</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.2000±0.0326</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.1085±0.0194</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.4750±0.0403</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.5466±0.0715</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.5827±0.0741</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.5580±0.0594</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.9595±0.0891</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.8199±0.1179</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7168±0.1158</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.7827±0.0386</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6401±0.0562</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.3744±0.0476</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.2016±0.0355</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.8119±0.0529</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.5470±0.0678</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.2515±0.0396</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.1196±0.0239</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.7564±0.0328</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7791±0.0573</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.7441±0.0422</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.6582±0.0400</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>0.8434±0.0216</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.7057±0.0428</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.3237±0.0487</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.0192±0.0120</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>0.5230±0.0421</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.3428±0.0678</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.0795±0.0298</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.0038±0.0059</t>
         </is>
@@ -917,100 +1577,320 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.3223±0.0509</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.2929±0.0877</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.2893±0.0417</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.2888±0.0541</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.9882±0.0022</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.9738±0.0051</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.9178±0.0089</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.7893±0.0104</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.8242±0.0621</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.5819±0.0855</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.2546±0.0496</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.1127±0.0215</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.7469±0.0421</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.6120±0.0880</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.3995±0.0724</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.3011±0.0451</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.7636±0.0479</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.5747±0.0793</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.2921±0.0537</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.1547±0.0264</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0.9476±0.0081</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0.8926±0.0153</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.7727±0.0149</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.6665±0.0133</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.7100±0.0438</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.5204±0.0732</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.2347±0.0463</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.1038±0.0182</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.4857±0.0561</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.4346±0.0560</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.2835±0.0358</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.1715±0.0263</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.5388±0.0884</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.4013±0.0514</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.2048±0.0322</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.1102±0.0201</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.4733±0.0396</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.5326±0.0770</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.5691±0.0718</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.5404±0.0680</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.9664±0.0832</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.8415±0.1146</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.7405±0.1197</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.7864±0.0362</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.6445±0.0549</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.3824±0.0491</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.2042±0.0366</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.8232±0.0529</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.5598±0.0673</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.2600±0.0417</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.1220±0.0250</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.7540±0.0315</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.7671±0.0615</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.7352±0.0412</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.6426±0.0391</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>0.8419±0.0233</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>0.7088±0.0433</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.3265±0.0502</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>0.0192±0.0120</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.5185±0.0476</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>0.3498±0.0690</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.0833±0.0328</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.0038±0.0055</t>
         </is>
@@ -1064,100 +1944,320 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.3203±0.0534</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.2825±0.0785</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.2860±0.0438</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.2812±0.0448</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.9879±0.0025</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.9728±0.0053</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.9139±0.0098</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.7808±0.0104</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.8215±0.0613</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.5734±0.0857</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.2482±0.0480</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.1108±0.0206</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.7492±0.0440</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.6178±0.0889</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.4022±0.0738</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.3077±0.0456</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.7633±0.0485</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.5727±0.0791</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.2875±0.0527</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.1536±0.0256</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.9463±0.0087</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0.8885±0.0166</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.7618±0.0150</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.6532±0.0126</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.7102±0.0443</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.5172±0.0724</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.2296±0.0452</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.1026±0.0177</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0.4846±0.0576</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.4370±0.0540</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.2796±0.0358</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.1708±0.0257</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.5311±0.0881</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.3969±0.0528</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.1992±0.0320</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.1086±0.0194</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.4750±0.0403</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.5465±0.0715</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.5810±0.0720</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.5610±0.0610</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.9608±0.0830</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.8191±0.1183</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.7161±0.1139</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.7827±0.0386</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.6397±0.0561</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.3740±0.0481</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.2020±0.0356</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.8119±0.0529</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.5466±0.0678</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.2513±0.0400</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.1198±0.0239</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.7564±0.0328</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.7785±0.0564</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.7436±0.0417</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.6600±0.0419</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>0.8434±0.0216</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>0.7060±0.0425</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.3237±0.0500</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>0.0189±0.0120</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.5230±0.0421</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>0.3434±0.0676</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.0796±0.0315</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.0035±0.0055</t>
         </is>
@@ -1211,100 +2311,320 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0.3715±0.0510</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.3552±0.0646</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.3421±0.0419</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.3176±0.0510</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.9857±0.0039</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.9713±0.0050</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.9089±0.0092</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.7721±0.0096</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.8346±0.0403</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.5849±0.0818</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.2465±0.0390</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.1163±0.0215</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.7181±0.0315</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.5699±0.0735</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.3555±0.0600</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.2881±0.0369</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.7458±0.0311</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.5508±0.0697</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.2697±0.0427</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0.1550±0.0256</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0.9406±0.0080</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0.8976±0.0126</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.8003±0.0119</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>0.7232±0.0120</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.6833±0.0294</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.4872±0.0622</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.2107±0.0326</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.1031±0.0179</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0.4747±0.0498</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.4215±0.0531</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.2667±0.0344</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.1662±0.0223</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.5451±0.0551</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.4197±0.0722</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.2007±0.0337</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.1091±0.0183</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.4543±0.0580</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.4764±0.0701</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.4877±0.0517</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.4805±0.0640</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.9901±0.0171</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.9069±0.0567</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.8234±0.0643</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.7562±0.0313</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.6243±0.0511</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.3613±0.0452</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1963±0.0325</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.8323±0.0349</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.5753±0.0675</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.2542±0.0408</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.1195±0.0225</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.6939±0.0373</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.6890±0.0558</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.6372±0.0459</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.5600±0.0381</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.8248±0.0359</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>0.6763±0.0350</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.2608±0.0441</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>0.0043±0.0058</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>0.4743±0.0407</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>0.2922±0.0559</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>0.0589±0.0187</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.0025±0.0042</t>
         </is>
@@ -1358,100 +2678,320 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.3518±0.0596</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.3307±0.0609</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.3058±0.0362</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.2641±0.0399</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.9856±0.0034</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.9682±0.0044</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.8939±0.0104</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.7241±0.0108</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.8280±0.0379</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.5582±0.0782</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.2130±0.0351</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.1018±0.0175</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.7328±0.0313</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.5868±0.0813</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.3727±0.0651</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.3292±0.0459</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.7531±0.0282</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.5447±0.0701</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.2527±0.0411</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.1475±0.0240</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.9404±0.0061</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.8884±0.0143</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0.7725±0.0112</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>0.6688±0.0106</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.6922±0.0238</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.4772±0.0608</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.1910±0.0302</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.0946±0.0160</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.4900±0.0375</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.4267±0.0540</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.2650±0.0349</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.1644±0.0233</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.5485±0.0510</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.4068±0.0734</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.1896±0.0307</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.1031±0.0171</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.4744±0.0516</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.5054±0.0671</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.5454±0.0617</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.5649±0.0591</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.9660±0.0572</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.8664±0.0640</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.7566±0.0748</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.7608±0.0264</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.6138±0.0503</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.3450±0.0427</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1889±0.0318</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.8131±0.0348</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.5401±0.0641</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.2320±0.0355</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.1110±0.0207</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.7159±0.0335</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.7178±0.0545</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.6836±0.0390</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.6438±0.0410</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>0.8264±0.0349</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>0.6614±0.0298</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.2363±0.0496</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.0031±0.0044</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>0.4838±0.0294</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>0.2693±0.0497</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.0404±0.0205</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.0012±0.0028</t>
         </is>
@@ -1505,100 +3045,320 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.3754±0.0482</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.3594±0.0674</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.3452±0.0434</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.3280±0.0540</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.9856±0.0039</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.9715±0.0049</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.9100±0.0092</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.7750±0.0097</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.8369±0.0383</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.5890±0.0821</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.2491±0.0395</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.1174±0.0216</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.7158±0.0296</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.5661±0.0721</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.3530±0.0578</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.2835±0.0355</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0.7453±0.0284</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.5507±0.0690</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.2705±0.0417</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0.1547±0.0251</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0.9403±0.0077</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>0.8983±0.0122</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0.8024±0.0114</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>0.7262±0.0117</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.6832±0.0276</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.4873±0.0610</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.2116±0.0318</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.1030±0.0176</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>0.4738±0.0500</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.4183±0.0534</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.2676±0.0326</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.1649±0.0214</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.5486±0.0544</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.4175±0.0646</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.2026±0.0328</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.1088±0.0178</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.4508±0.0580</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.4704±0.0713</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.4846±0.0485</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.4694±0.0637</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.9923±0.0146</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.9094±0.0546</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.8286±0.0622</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.7543±0.0291</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.6241±0.0496</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.3623±0.0431</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.1951±0.0313</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.8341±0.0324</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.5791±0.0675</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.2560±0.0399</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>0.1190±0.0217</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.6894±0.0363</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0.6833±0.0534</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.6320±0.0431</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.5503±0.0373</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>0.8264±0.0359</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.6760±0.0344</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.2617±0.0435</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0.0047±0.0058</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>0.4788±0.0420</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>0.2916±0.0520</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.0600±0.0186</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.0028±0.0043</t>
         </is>
@@ -1652,100 +3412,320 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0.3532±0.0591</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.3301±0.0613</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.3076±0.0335</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.2646±0.0358</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.9856±0.0036</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.9684±0.0043</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.8945±0.0104</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.7257±0.0107</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.8274±0.0377</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.5578±0.0771</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.2139±0.0360</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.1020±0.0180</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.7328±0.0353</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.5864±0.0773</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.3707±0.0650</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.3280±0.0474</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.7532±0.0310</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.5442±0.0670</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.2532±0.0419</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.1475±0.0247</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.9407±0.0069</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.8885±0.0133</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.7730±0.0114</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>0.6695±0.0103</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.6932±0.0278</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.4769±0.0579</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.1918±0.0316</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.0947±0.0165</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.4891±0.0424</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.4252±0.0540</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.2628±0.0340</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.1644±0.0242</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.5520±0.0537</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.4048±0.0736</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.1884±0.0304</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.1033±0.0179</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.4748±0.0569</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.5049±0.0683</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.5393±0.0589</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.5636±0.0562</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.9629±0.0621</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.8728±0.0682</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.7515±0.0883</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.7618±0.0296</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.6139±0.0475</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.3449±0.0428</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1891±0.0328</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.8153±0.0340</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.5402±0.0619</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.2323±0.0358</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.1112±0.0213</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.7162±0.0394</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.7182±0.0536</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.6809±0.0404</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.6406±0.0442</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>0.8279±0.0351</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>0.6626±0.0288</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.2372±0.0515</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0.0031±0.0044</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>0.4860±0.0333</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>0.2689±0.0467</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.0417±0.0223</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.0012±0.0028</t>
         </is>
